--- a/resources/templates/standard/J1100-09.xlsx
+++ b/resources/templates/standard/J1100-09.xlsx
@@ -14,7 +14,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+  <si>
+    <t>{{companyLogo}}</t>
+  </si>
   <si>
     <t>제조 타당성 검토서</t>
   </si>
@@ -583,12 +586,14 @@
   </cols>
   <sheetData>
     <row r="1" ht="20.15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
-      <c r="A1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
       <c r="D1" s="1"/>
       <c r="E1" s="2" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
@@ -608,20 +613,20 @@
       <c r="U1" s="2"/>
       <c r="V1" s="2"/>
       <c r="W1" s="3" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X1" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y1" s="4"/>
       <c r="Z1" s="4"/>
       <c r="AA1" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AB1" s="4"/>
       <c r="AC1" s="4"/>
       <c r="AD1" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE1" s="4"/>
       <c r="AF1" s="4"/>
@@ -696,7 +701,7 @@
     </row>
     <row r="4" ht="20.15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" s="6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -714,7 +719,7 @@
       <c r="O4" s="7"/>
       <c r="P4" s="7"/>
       <c r="Q4" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="R4" s="4"/>
       <c r="S4" s="4"/>
@@ -734,7 +739,7 @@
     </row>
     <row r="5" ht="20.15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" s="8"/>
       <c r="C5" s="8"/>
@@ -752,7 +757,7 @@
       <c r="O5" s="5"/>
       <c r="P5" s="5"/>
       <c r="Q5" s="9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="R5" s="9"/>
       <c r="S5" s="9"/>
@@ -772,7 +777,7 @@
     </row>
     <row r="6" ht="20.15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
@@ -790,7 +795,7 @@
       <c r="O6" s="5"/>
       <c r="P6" s="5"/>
       <c r="Q6" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R6" s="9"/>
       <c r="S6" s="9"/>
@@ -810,7 +815,7 @@
     </row>
     <row r="7" ht="20.15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B7" s="8"/>
       <c r="C7" s="8"/>
@@ -823,7 +828,7 @@
       <c r="J7" s="8"/>
       <c r="K7" s="8"/>
       <c r="L7" s="9" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M7" s="9"/>
       <c r="N7" s="9"/>
@@ -835,7 +840,7 @@
       <c r="T7" s="9"/>
       <c r="U7" s="9"/>
       <c r="V7" s="9" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="W7" s="9"/>
       <c r="X7" s="9"/>
@@ -1054,7 +1059,7 @@
     </row>
     <row r="14" ht="20.15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B14" s="11"/>
       <c r="C14" s="11"/>
@@ -1124,7 +1129,7 @@
     </row>
     <row r="16" ht="20.15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B16" s="11"/>
       <c r="C16" s="11"/>
@@ -1194,7 +1199,7 @@
     </row>
     <row r="18" ht="20.15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B18" s="11"/>
       <c r="C18" s="11"/>
@@ -1332,7 +1337,7 @@
     </row>
     <row r="22" ht="20.15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B22" s="11"/>
       <c r="C22" s="11"/>
@@ -1402,7 +1407,7 @@
     </row>
     <row r="24" ht="20.15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B24" s="11"/>
       <c r="C24" s="11"/>
@@ -1472,7 +1477,7 @@
     </row>
     <row r="26" ht="20.15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B26" s="11"/>
       <c r="C26" s="11"/>
@@ -1542,7 +1547,7 @@
     </row>
     <row r="28" ht="20.15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B28" s="11"/>
       <c r="C28" s="11"/>
@@ -1612,7 +1617,7 @@
     </row>
     <row r="30" ht="20.15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B30" s="11"/>
       <c r="C30" s="11"/>
@@ -1682,7 +1687,7 @@
     </row>
     <row r="32" ht="20.15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B32" s="11"/>
       <c r="C32" s="11"/>
@@ -1752,13 +1757,13 @@
     </row>
     <row r="34" ht="20.15" customHeight="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B34" s="12"/>
       <c r="C34" s="12"/>
       <c r="D34" s="12"/>
       <c r="E34" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F34" s="9"/>
       <c r="G34" s="9"/>
@@ -1774,7 +1779,7 @@
       <c r="Q34" s="5"/>
       <c r="R34" s="5"/>
       <c r="S34" s="9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="T34" s="9"/>
       <c r="U34" s="9"/>
@@ -1796,7 +1801,7 @@
       <c r="C35" s="12"/>
       <c r="D35" s="12"/>
       <c r="E35" s="9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F35" s="9"/>
       <c r="G35" s="9"/>
@@ -1812,7 +1817,7 @@
       <c r="Q35" s="5"/>
       <c r="R35" s="5"/>
       <c r="S35" s="9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="T35" s="9"/>
       <c r="U35" s="9"/>
@@ -1834,7 +1839,7 @@
       <c r="C36" s="12"/>
       <c r="D36" s="12"/>
       <c r="E36" s="13" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F36" s="13"/>
       <c r="G36" s="13"/>
